--- a/output/pdf_financials_xlsx/USLI.xlsx
+++ b/output/pdf_financials_xlsx/USLI.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.155964</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.20061</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.40663</v>
       </c>
     </row>
     <row r="93">
@@ -2980,7 +2980,11 @@
           <t>Share-based payments reserve (note 9)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3306,7 +3310,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.155964</v>
       </c>

--- a/output/pdf_financials_xlsx/USLI.xlsx
+++ b/output/pdf_financials_xlsx/USLI.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.040809</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.084838</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.004542</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.040809</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.084838</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.004542</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.040809</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.6538119999999999</v>
+        <v>0.568974</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.130209</v>
+        <v>0.125667</v>
       </c>
     </row>
     <row r="49">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/USLI.xlsx
+++ b/output/pdf_financials_xlsx/USLI.xlsx
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.000693</v>
+        <v>0.021562</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.0056</v>
+        <v>0.055371</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.010047</v>
+        <v>0.06404700000000001</v>
       </c>
     </row>
     <row r="10">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.055601</v>
+        <v>0.07647</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.540493</v>
+        <v>0.590264</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.67525</v>
+        <v>0.72925</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.055601</v>
+        <v>-0.07647</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.540493</v>
+        <v>-0.590264</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.67525</v>
+        <v>-0.72925</v>
       </c>
     </row>
     <row r="12">
@@ -5334,7 +5334,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -5681,7 +5685,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E96" s="5" t="n">
         <v>0.020869</v>
       </c>

--- a/output/pdf_financials_xlsx/USLI.xlsx
+++ b/output/pdf_financials_xlsx/USLI.xlsx
@@ -1513,10 +1513,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.5065</v>
       </c>
     </row>
     <row r="68">
